--- a/output/pdf_financials_xlsx/AAN.xlsx
+++ b/output/pdf_financials_xlsx/AAN.xlsx
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.7010420000000001</v>
+        <v>-0.7010420000000001</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>5.94876</v>
+        <v>-5.94876</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-2.46588</v>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.7010420000000001</v>
+        <v>-0.7010420000000001</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>5.94876</v>
+        <v>-5.94876</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-2.46588</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.7010420000000001</v>
+        <v>-0.7010420000000001</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5.94876</v>
+        <v>-5.94876</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-2.46588</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-424.911429</v>
+        <v>424.911429</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>123.294</v>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.7010420000000001</v>
+        <v>-0.7010420000000001</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>5.94876</v>
+        <v>-5.94876</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-2.46588</v>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.742946</v>
+        <v>-0.659138</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>6.037272</v>
+        <v>-5.860248</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-2.371045</v>
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -6339,52 +6339,52 @@
         <v>0.016511</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.265874</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.28228</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.420507</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.730539</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.20261</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.538678</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.840907</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.239609</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.862406</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.979195</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.017858</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.814814</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>6.064802</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>7.406673</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>5.434332</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>5.535444</v>
       </c>
     </row>
     <row r="93">
@@ -10630,7 +10630,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -11782,7 +11786,11 @@
           <t>Share-based payment reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -13008,7 +13016,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -13828,7 +13840,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -14636,7 +14652,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -15256,7 +15276,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -17042,7 +17066,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -18844,7 +18872,11 @@
           <t>Reserve (note 11)</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -20326,7 +20358,11 @@
           <t>Reserves 282,280</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -52502,7 +52538,7 @@
         </is>
       </c>
       <c r="G415" s="5" t="n">
-        <v>0.7010420000000001</v>
+        <v>-0.7010420000000001</v>
       </c>
       <c r="H415" s="5" t="n">
         <v>-1.371856</v>
@@ -60299,10 +60335,10 @@
         </is>
       </c>
       <c r="H490" s="5" t="n">
-        <v>5.94876</v>
+        <v>-5.94876</v>
       </c>
       <c r="I490" s="5" t="n">
-        <v>2.46588</v>
+        <v>-2.46588</v>
       </c>
       <c r="J490" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/AAN.xlsx
+++ b/output/pdf_financials_xlsx/AAN.xlsx
@@ -1101,10 +1101,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C12" s="3" t="n">
+        <v>0.004363</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1152,7 +1150,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.031593</v>
       </c>
     </row>
     <row r="13">
@@ -2201,7 +2199,7 @@
         <v>-9.87274</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-12.853222</v>
+        <v>-12.884815</v>
       </c>
     </row>
     <row r="28">
@@ -2329,7 +2327,7 @@
         <v>-9.813312</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-12.776259</v>
+        <v>-12.807852</v>
       </c>
     </row>
     <row r="30">
@@ -2605,10 +2603,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.015389</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.08647000000000001</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>2.085541</v>
@@ -2623,40 +2621,40 @@
         <v>0.106355</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.018922</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.830473</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>3.048439</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.034113</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.08740299999999999</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.051445</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.032425</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.08226600000000001</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.116551</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.453283</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>1.274003</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.345655</v>
       </c>
     </row>
     <row r="35">
@@ -2727,10 +2725,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.525088</v>
+        <v>0.540477</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.38064</v>
+        <v>0.46711</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>2.085541</v>
@@ -2745,40 +2743,40 @@
         <v>0.106355</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.018922</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.830473</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>3.048439</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.034113</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.08740299999999999</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.051445</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.032425</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.08226600000000001</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.116551</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.453283</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>1.274003</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.345655</v>
       </c>
     </row>
     <row r="37">
@@ -3459,10 +3457,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.031907</v>
+        <v>0.016518</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.087338</v>
+        <v>0.000868</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.021808</v>
@@ -3477,40 +3475,40 @@
         <v>0.00675</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.023566</v>
+        <v>0.004644</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.839116</v>
+        <v>0.008643</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3.191766</v>
+        <v>0.143327</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.078801</v>
+        <v>0.044688</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.399137</v>
+        <v>0.311734</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.080986</v>
+        <v>0.029541</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.053809</v>
+        <v>0.021384</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.341898</v>
+        <v>0.259632</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.402849</v>
+        <v>0.286298</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.588269</v>
+        <v>0.134986</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>1.39853</v>
+        <v>0.124527</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>2.556035</v>
+        <v>2.21038</v>
       </c>
     </row>
     <row r="49">
@@ -8350,16 +8348,16 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.03598</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.035952</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.043069</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.046783</v>
       </c>
       <c r="Q124" s="3" t="n">
         <v>0</v>
@@ -8413,16 +8411,16 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.03598</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.035952</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.043069</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.046783</v>
       </c>
       <c r="Q125" s="3" t="n">
         <v>0</v>
@@ -9254,7 +9252,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -20884,7 +20882,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
@@ -27970,7 +27968,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -30308,7 +30310,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -36806,7 +36812,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -52308,7 +52318,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -54060,7 +54070,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -55190,7 +55200,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -61162,7 +61172,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">

--- a/output/pdf_financials_xlsx/AAN.xlsx
+++ b/output/pdf_financials_xlsx/AAN.xlsx
@@ -822,10 +822,10 @@
         <v>0.215328</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.90479</v>
+        <v>0.94979</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.447586</v>
+        <v>0.492586</v>
       </c>
     </row>
     <row r="8">
@@ -1017,10 +1017,10 @@
         <v>0.215328</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.90479</v>
+        <v>0.94979</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.447586</v>
+        <v>0.492586</v>
       </c>
     </row>
     <row r="11">
@@ -4713,10 +4713,10 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.07509</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.106585</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0</v>
@@ -7460,22 +7460,22 @@
         <v>0</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.000654</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.066026</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>1.695133</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.777625</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>2.743644</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.495081</v>
       </c>
       <c r="S110" s="3" t="n">
         <v>0</v>
@@ -7514,10 +7514,10 @@
         <v>0</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.050914</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.016444</v>
       </c>
       <c r="L111" s="3" t="n">
         <v>0</v>
@@ -7535,13 +7535,13 @@
         <v>0</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>-0.035585</v>
       </c>
       <c r="R111" s="3" t="n">
-        <v>0</v>
+        <v>-0.08640299999999999</v>
       </c>
       <c r="S111" s="3" t="n">
-        <v>0</v>
+        <v>-0.137239</v>
       </c>
     </row>
     <row r="112">
@@ -9003,10 +9003,10 @@
         <v>0</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.050914</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.016444</v>
       </c>
       <c r="L134" s="3" t="n">
         <v>0</v>
@@ -9024,13 +9024,13 @@
         <v>0</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-0.035585</v>
       </c>
       <c r="R134" s="3" t="n">
-        <v>0</v>
+        <v>-0.08640299999999999</v>
       </c>
       <c r="S134" s="3" t="n">
-        <v>0</v>
+        <v>-0.137239</v>
       </c>
     </row>
     <row r="135">
@@ -9072,10 +9072,10 @@
         </is>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-3.844359</v>
+        <v>-3.895273</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-3.497882</v>
+        <v>-3.514326</v>
       </c>
       <c r="L135" s="3" t="n">
         <v>-4.302898</v>
@@ -9093,13 +9093,13 @@
         <v>-6.708182</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>-5.811683</v>
+        <v>-5.847268</v>
       </c>
       <c r="R135" s="3" t="n">
-        <v>-7.358842</v>
+        <v>-7.445245</v>
       </c>
       <c r="S135" s="3" t="n">
-        <v>-8.950307</v>
+        <v>-9.087546</v>
       </c>
     </row>
   </sheetData>
@@ -22340,7 +22340,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -22900,7 +22904,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -25746,7 +25754,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -27752,7 +27764,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -32412,7 +32428,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -35772,7 +35792,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -39018,7 +39042,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -51374,7 +51402,11 @@
           <t>Directors’ fee (Note 8)</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E403" t="inlineStr">
         <is>
           <t>-</t>
